--- a/new_species.xlsx
+++ b/new_species.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Celia Dawn\Documents\Roms\Decomps\celias-stupid-repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB05D705-B479-4164-BD59-0566448FE66D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A76404-1A1D-418C-A5E2-A87CC7424F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D4D9E477-37BF-4694-B23F-30E3AB73FF9F}"/>
   </bookViews>
